--- a/okr_backup.xlsx
+++ b/okr_backup.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,7 +484,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -499,72 +499,23 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Atingir 90% dos índices de Governança do Questionário iESGO (TCU)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>João Silva</t>
-        </is>
-      </c>
+          <t>Atingir 80% dos índices de Governança do Questionário iESGO (TCU)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2025-01-07</t>
+          <t>2025-01-01</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-12-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Estratégico</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Melhorar o índice de satisfação dos usuários para 85%</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ana Paula</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2025-01-07</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-12-31</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -579,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -650,7 +601,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -665,7 +616,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Atingir 90% dos índices de Governança do Questionário iESGO (TCU)</t>
+          <t>Atingir 80% dos índices de Governança do Questionário iESGO (TCU)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -675,7 +626,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Identificar os pontos de melhoria</t>
+          <t>Identificar 100% dos pontos ainda não implementados</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -684,19 +635,15 @@
       <c r="I2" t="n">
         <v>100</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Maria Souza</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -706,7 +653,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,7 +668,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Atingir 90% dos índices de Governança do Questionário iESGO (TCU)</t>
+          <t>Atingir 80% dos índices de Governança do Questionário iESGO (TCU)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -731,20 +678,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Implantar 90% dos pontos de melhorias do iESGO</t>
+          <t>Implantar, no mínimo, 80% dos pontos de melhorias do IESGO específicos do NEGI</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Lucas Lima</t>
-        </is>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>2025-12-31</t>
@@ -752,7 +695,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -762,7 +705,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -777,7 +720,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Atingir 90% dos índices de Governança do Questionário iESGO (TCU)</t>
+          <t>Atingir 80% dos índices de Governança do Questionário iESGO (TCU)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -787,7 +730,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Estabelecer plano de ação para os demais Núcleos</t>
+          <t>Estabelecer um plano de ação para incentivar os 8 Núcleos da Administração a implantar, no mínimo, 70% dos pontos de melhorias do IESGO</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -796,131 +739,15 @@
       <c r="I4" t="n">
         <v>8</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Rafael Costa</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Estratégico</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Melhorar o índice de satisfação dos usuários para 85%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>KR 2.1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Implementar pesquisa de satisfação trimestral</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Carla Dias</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Estratégico</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Melhorar o índice de satisfação dos usuários para 85%</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>KR 2.2</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Reduzir tempo médio de resposta a demandas para 3 dias úteis</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>10</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Diego Melo</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -935,7 +762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,7 +818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1001,32 +828,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KR 1.1</t>
+          <t>KR 1.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2.1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Avaliar e priorizar os pontos de melhoria identificados</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Carlos</t>
-        </is>
-      </c>
+          <t>Executar as iniciativas relativas à Governança</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Não Iniciado</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -1036,7 +859,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1046,32 +869,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KR 1.1</t>
+          <t>KR 1.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.2.2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Classificar os pontos de melhorias por relevância</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ana</t>
-        </is>
-      </c>
+          <t>Criar um Programa de Integridade com novas 07 iniciativas previstas no IESGO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Não Iniciado</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -1081,7 +900,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1091,32 +910,28 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KR 1.1</t>
+          <t>KR 1.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.2.3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Desenvolver um cronograma de implantação</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Pedro</t>
-        </is>
-      </c>
+          <t>Atualizar a Política de gestão de riscos com 10 iniciativas previstas no IESGO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Não Iniciado</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -1126,7 +941,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1141,19 +956,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.2.4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Executar plano de implantação</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Lucas</t>
-        </is>
-      </c>
+          <t>Implantar RELATÓRIO que contemple os itens do IESGO relativos à gestão estratégica</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>Não Iniciado</t>
@@ -1161,7 +972,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -1171,7 +982,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1181,24 +992,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KR 1.2</t>
+          <t>KR 1.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3.1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitorar execução quinzenal</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Fernanda</t>
-        </is>
-      </c>
+          <t>Plano - PA 0004127-57.2024.4.05.7600, inserido relatório de melhorias aos Núcleos e Seções</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>Não Iniciado</t>
@@ -1206,7 +1013,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1023,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1231,27 +1038,23 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1.3.2</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Reunião com líderes dos núcleos</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Rafael</t>
-        </is>
-      </c>
+          <t>Elaborar planilha de acompanhamento das ações do iESGO aos Núcleos envolvidos</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Concluído</t>
+          <t>Não Iniciado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1064,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TESTE</t>
+          <t>NEGI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1276,252 +1079,23 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.3.3</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Elaborar guia de boas práticas</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Juliana</t>
-        </is>
-      </c>
+          <t>Encaminhar planilha de acompanhamento aos Núcleos envolvidos no iESGO a partir do PA 0004127-57.2024.4.05.7600</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Não Iniciado</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>KR 2.1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Criar formulário de pesquisa</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Carla</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>KR 2.1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Aplicar 1ª rodada de pesquisa</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Bruno</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>KR 2.1</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Analisar resultados e propor melhorias</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Carla</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>KR 2.2</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Mapear fluxo atual de demandas</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Diego</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Concluído</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>KR 2.2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Implementar sistema de triagem</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Patrícia</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
+          <t>2026-03-03 00:23:20</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1591,342 +1165,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OKR 1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>KR 1.1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Semana 09/2025</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>96</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Quase concluído</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OKR 1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>KR 1.1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2025-02-05</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Semana 06/2025</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>70</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Priorização em andamento</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OKR 1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>KR 1.1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2025-01-15</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Semana 03/2025</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>40</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Levantamento inicial concluído</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OKR 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>KR 1.2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Semana 09/2025</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Início do plano de implantação</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OKR 1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>KR 1.3</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Semana 09/2025</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4 de 8 núcleos engajados</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>KR 2.1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Semana 09/2025</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1ª pesquisa aplicada</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TESTE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>OKR 2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>KR 2.2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Semana 09/2025</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Em Andamento</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Reduzindo gradualmente</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-03-02 15:17:20</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
